--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T15:33:45+00:00</t>
+    <t>2024-12-11T16:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T16:17:48+00:00</t>
+    <t>2024-12-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -51,7 +51,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:55:45+00:00</t>
+    <t>2024-12-23T16:34:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -36,9 +36,15 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Conditions</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
+    <t>Antimicrobiology - Vaginitis-related conditions</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -48,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T16:34:43+00:00</t>
+    <t>2025-01-04T23:12:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,6 +87,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Antimicrobiology - S2 Get data to collect - Response - 1.4. ValueSet</t>
+  </si>
+  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -114,13 +126,13 @@
     <t>1</t>
   </si>
   <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>419760006</t>
   </si>
   <si>
     <t>Bacterial vaginosis</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>276877003</t>
@@ -301,92 +313,100 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -401,82 +421,88 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T23:12:19+00:00</t>
+    <t>2025-01-05T07:31:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-05T07:31:05+00:00</t>
+    <t>2025-01-10T09:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-10T09:03:58+00:00</t>
+    <t>2025-01-24T08:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T08:18:33+00:00</t>
+    <t>2025-01-28T16:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T16:43:38+00:00</t>
+    <t>2025-01-30T12:44:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T12:44:56+00:00</t>
+    <t>2025-01-30T13:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T13:04:50+00:00</t>
+    <t>2025-01-31T16:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T16:23:22+00:00</t>
+    <t>2025-02-03T12:16:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T12:16:06+00:00</t>
+    <t>2025-02-07T08:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T08:52:52+00:00</t>
+    <t>2025-02-17T11:04:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:04:00+00:00</t>
+    <t>2025-02-17T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:10:24+00:00</t>
+    <t>2025-02-17T11:11:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:11:10+00:00</t>
+    <t>2025-02-17T11:11:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:11:18+00:00</t>
+    <t>2025-02-17T11:12:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:12:19+00:00</t>
+    <t>2025-02-17T11:14:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:14:25+00:00</t>
+    <t>2025-02-17T11:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T11:15:32+00:00</t>
+    <t>2025-02-19T10:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T10:40:21+00:00</t>
+    <t>2025-02-26T15:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:33:36+00:00</t>
+    <t>2025-02-26T15:37:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:37:29+00:00</t>
+    <t>2025-02-27T22:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/condition-valueset</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/condition-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-condition-valueset.xlsx
+++ b/ValueSet-condition-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
